--- a/exports/trend_1d/MANAPPURAM_full_report.xlsx
+++ b/exports/trend_1d/MANAPPURAM_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:U71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>9.81</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42089</v>
+        <v>42090</v>
       </c>
       <c r="H2" t="n">
-        <v>32.29</v>
+        <v>31.75</v>
       </c>
       <c r="I2" t="n">
         <v>31.75530786797679</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K2" t="n">
-        <v>-4.75</v>
+        <v>-6.34</v>
       </c>
       <c r="L2" t="n">
         <v>8.26</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>14.63</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42261</v>
+        <v>42262</v>
       </c>
       <c r="H3" t="n">
-        <v>22.7</v>
+        <v>24.35</v>
       </c>
       <c r="I3" t="n">
         <v>24.19828133551101</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K3" t="n">
-        <v>28.5</v>
+        <v>23.31</v>
       </c>
       <c r="L3" t="n">
         <v>23.75</v>
@@ -612,7 +647,7 @@
         <v>5.92</v>
       </c>
       <c r="N3" t="n">
-        <v>6.73</v>
+        <v>7.27</v>
       </c>
       <c r="O3" t="n">
         <v>-1.67</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>118</v>
+        <v>119</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>6</v>
+      </c>
+      <c r="U3" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>21.48</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42317</v>
+        <v>42318</v>
       </c>
       <c r="H4" t="n">
-        <v>22.75</v>
+        <v>22.55</v>
       </c>
       <c r="I4" t="n">
         <v>22.63387075710304</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K4" t="n">
-        <v>-6.57</v>
+        <v>-7.39</v>
       </c>
       <c r="L4" t="n">
         <v>10.27</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42271</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>14.55</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42332</v>
+        <v>42334</v>
       </c>
       <c r="H5" t="n">
-        <v>22.25</v>
+        <v>25.2</v>
       </c>
       <c r="I5" t="n">
         <v>24.81344865388499</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K5" t="n">
-        <v>1.33</v>
+        <v>-11.75</v>
       </c>
       <c r="L5" t="n">
-        <v>5.32</v>
+        <v>13.53</v>
       </c>
       <c r="M5" t="n">
         <v>1.55</v>
       </c>
       <c r="N5" t="n">
-        <v>3.99</v>
+        <v>13.26</v>
       </c>
       <c r="O5" t="n">
         <v>-0.88</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>17.31</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42684</v>
+        <v>42685</v>
       </c>
       <c r="H6" t="n">
-        <v>102.1</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="I6" t="n">
         <v>92.03125788727547</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K6" t="n">
-        <v>305.16</v>
+        <v>257.54</v>
       </c>
       <c r="L6" t="n">
         <v>11.71</v>
@@ -783,7 +854,7 @@
         <v>15.33</v>
       </c>
       <c r="N6" t="n">
-        <v>9.23</v>
+        <v>11.75</v>
       </c>
       <c r="O6" t="n">
         <v>13.26</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>236</v>
+        <v>237</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>12</v>
+      </c>
+      <c r="U6" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>26.08</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42737</v>
+        <v>42738</v>
       </c>
       <c r="H7" t="n">
-        <v>68.95</v>
+        <v>72.7</v>
       </c>
       <c r="I7" t="n">
         <v>70.53079612325148</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K7" t="n">
-        <v>23.47</v>
+        <v>19.31</v>
       </c>
       <c r="L7" t="n">
         <v>10.65</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>18.09</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42803</v>
+        <v>42804</v>
       </c>
       <c r="H8" t="n">
-        <v>94.65000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="I8" t="n">
         <v>91.86479548101823</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K8" t="n">
-        <v>30.19</v>
+        <v>24.48</v>
       </c>
       <c r="L8" t="n">
         <v>6.4</v>
       </c>
       <c r="M8" t="n">
-        <v>1.12</v>
+        <v>4.91</v>
       </c>
       <c r="N8" t="n">
-        <v>4.2</v>
+        <v>4.38</v>
       </c>
       <c r="O8" t="n">
         <v>5.44</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>11.58</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42821</v>
+        <v>42822</v>
       </c>
       <c r="H9" t="n">
-        <v>98.65000000000001</v>
+        <v>101.55</v>
       </c>
       <c r="I9" t="n">
         <v>99.62993897130791</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K9" t="n">
-        <v>-9.01</v>
+        <v>-12.21</v>
       </c>
       <c r="L9" t="n">
-        <v>10.11</v>
+        <v>13.26</v>
       </c>
       <c r="M9" t="n">
         <v>3.65</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>11.59</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42873</v>
+        <v>42874</v>
       </c>
       <c r="H10" t="n">
-        <v>90.7</v>
+        <v>89.65000000000001</v>
       </c>
       <c r="I10" t="n">
         <v>89.77890704092488</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K10" t="n">
-        <v>-10.68</v>
+        <v>-11.72</v>
       </c>
       <c r="L10" t="n">
-        <v>11.87</v>
+        <v>11.96</v>
       </c>
       <c r="M10" t="n">
         <v>0.86</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>10.75</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42893</v>
+        <v>42894</v>
       </c>
       <c r="H11" t="n">
-        <v>92.3</v>
+        <v>94.5</v>
       </c>
       <c r="I11" t="n">
         <v>94.08165625561529</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.96</v>
+        <v>-5.41</v>
       </c>
       <c r="L11" t="n">
-        <v>5.47</v>
+        <v>7.03</v>
       </c>
       <c r="M11" t="n">
         <v>4.28</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>10.36</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42956</v>
+        <v>42957</v>
       </c>
       <c r="H12" t="n">
-        <v>98.7</v>
+        <v>93.3</v>
       </c>
       <c r="I12" t="n">
         <v>98.35426600844944</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K12" t="n">
-        <v>4.44</v>
+        <v>-1.27</v>
       </c>
       <c r="L12" t="n">
-        <v>2.96</v>
+        <v>4.66</v>
       </c>
       <c r="M12" t="n">
         <v>1.49</v>
       </c>
       <c r="N12" t="n">
-        <v>5.41</v>
+        <v>5.47</v>
       </c>
       <c r="O12" t="n">
         <v>2.38</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>14.61</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42977</v>
+        <v>42978</v>
       </c>
       <c r="H13" t="n">
-        <v>95.75</v>
+        <v>99.3</v>
       </c>
       <c r="I13" t="n">
         <v>98.53850867324428</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.63</v>
+        <v>-6.43</v>
       </c>
       <c r="L13" t="n">
-        <v>5.52</v>
+        <v>6.91</v>
       </c>
       <c r="M13" t="n">
         <v>3.07</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>16.65</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43000</v>
+        <v>43003</v>
       </c>
       <c r="H14" t="n">
-        <v>99.55</v>
+        <v>96.2</v>
       </c>
       <c r="I14" t="n">
         <v>96.63997663521862</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K14" t="n">
-        <v>0.25</v>
+        <v>-3.12</v>
       </c>
       <c r="L14" t="n">
-        <v>4.53</v>
+        <v>5.99</v>
       </c>
       <c r="M14" t="n">
         <v>1.89</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>14.43</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43062</v>
+        <v>43063</v>
       </c>
       <c r="H15" t="n">
-        <v>102.4</v>
+        <v>106.7</v>
       </c>
       <c r="I15" t="n">
         <v>105.8314030823174</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K15" t="n">
-        <v>-6.44</v>
+        <v>-10.91</v>
       </c>
       <c r="L15" t="n">
-        <v>11.12</v>
+        <v>11.33</v>
       </c>
       <c r="M15" t="n">
         <v>1.97</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>13.5</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43132</v>
+        <v>43133</v>
       </c>
       <c r="H16" t="n">
-        <v>116.05</v>
+        <v>106.25</v>
       </c>
       <c r="I16" t="n">
         <v>110.2093552446647</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K16" t="n">
-        <v>8.76</v>
+        <v>-0.42</v>
       </c>
       <c r="L16" t="n">
         <v>9.84</v>
@@ -1353,7 +1544,7 @@
         <v>1.97</v>
       </c>
       <c r="N16" t="n">
-        <v>4.45</v>
+        <v>8.44</v>
       </c>
       <c r="O16" t="n">
         <v>4.2</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>4</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>18.56</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43192</v>
+        <v>43193</v>
       </c>
       <c r="H17" t="n">
-        <v>112.55</v>
+        <v>114.4</v>
       </c>
       <c r="I17" t="n">
         <v>113.6053074469589</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K17" t="n">
-        <v>-5.93</v>
+        <v>-7.67</v>
       </c>
       <c r="L17" t="n">
-        <v>7.11</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="M17" t="n">
         <v>2.39</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>10.19</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43234</v>
+        <v>43235</v>
       </c>
       <c r="H18" t="n">
-        <v>119.65</v>
+        <v>115.1</v>
       </c>
       <c r="I18" t="n">
         <v>116.3355553164215</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K18" t="n">
-        <v>4.59</v>
+        <v>0.61</v>
       </c>
       <c r="L18" t="n">
         <v>2.27</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>14.18</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43313</v>
+        <v>43314</v>
       </c>
       <c r="H19" t="n">
-        <v>105.35</v>
+        <v>109.45</v>
       </c>
       <c r="I19" t="n">
         <v>107.1954643689875</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K19" t="n">
-        <v>8.470000000000001</v>
+        <v>4.91</v>
       </c>
       <c r="L19" t="n">
         <v>6.21</v>
@@ -1524,7 +1751,7 @@
         <v>1.55</v>
       </c>
       <c r="N19" t="n">
-        <v>2.97</v>
+        <v>3.89</v>
       </c>
       <c r="O19" t="n">
         <v>-3.8</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>11.46</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43328</v>
+        <v>43329</v>
       </c>
       <c r="H20" t="n">
-        <v>102.6</v>
+        <v>100.85</v>
       </c>
       <c r="I20" t="n">
         <v>102.2600007882332</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K20" t="n">
-        <v>-6.26</v>
+        <v>-7.86</v>
       </c>
       <c r="L20" t="n">
-        <v>7.17</v>
+        <v>8.73</v>
       </c>
       <c r="M20" t="n">
         <v>0.75</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>11.22</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43405</v>
+        <v>43406</v>
       </c>
       <c r="H21" t="n">
-        <v>78.45</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="I21" t="n">
         <v>81.8837158064734</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K21" t="n">
-        <v>22.21</v>
+        <v>17.8</v>
       </c>
       <c r="L21" t="n">
         <v>2.97</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>18.22</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43493</v>
+        <v>43494</v>
       </c>
       <c r="H22" t="n">
-        <v>95.90000000000001</v>
+        <v>90.95</v>
       </c>
       <c r="I22" t="n">
         <v>91.01777753816125</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K22" t="n">
-        <v>15.68</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="L22" t="n">
         <v>6.33</v>
@@ -1695,7 +1958,7 @@
         <v>3.02</v>
       </c>
       <c r="N22" t="n">
-        <v>3.87</v>
+        <v>5.16</v>
       </c>
       <c r="O22" t="n">
         <v>5.67</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>12.51</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43502</v>
+        <v>43503</v>
       </c>
       <c r="H23" t="n">
-        <v>96.90000000000001</v>
+        <v>104.05</v>
       </c>
       <c r="I23" t="n">
         <v>99.94919017468044</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K23" t="n">
-        <v>-6.54</v>
+        <v>-14.4</v>
       </c>
       <c r="L23" t="n">
-        <v>7.75</v>
+        <v>16.33</v>
       </c>
       <c r="M23" t="n">
-        <v>0.11</v>
+        <v>4.23</v>
       </c>
       <c r="N23" t="n">
-        <v>3.3</v>
+        <v>7.38</v>
       </c>
       <c r="O23" t="n">
         <v>-5.16</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>14.13</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43593</v>
+        <v>43594</v>
       </c>
       <c r="H24" t="n">
-        <v>114.9</v>
+        <v>112.9</v>
       </c>
       <c r="I24" t="n">
         <v>114.6735306122455</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K24" t="n">
-        <v>10.43</v>
+        <v>8.51</v>
       </c>
       <c r="L24" t="n">
         <v>6.54</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1845,25 +2144,25 @@
         <v>10.93</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43602</v>
+        <v>43605</v>
       </c>
       <c r="H25" t="n">
-        <v>122.6</v>
+        <v>125.45</v>
       </c>
       <c r="I25" t="n">
         <v>125.2414411773581</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K25" t="n">
-        <v>-8.59</v>
+        <v>-11.12</v>
       </c>
       <c r="L25" t="n">
         <v>12.36</v>
       </c>
       <c r="M25" t="n">
-        <v>1.28</v>
+        <v>2.2</v>
       </c>
       <c r="N25" t="n">
         <v>6.71</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>11.55</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43664</v>
+        <v>43665</v>
       </c>
       <c r="H26" t="n">
-        <v>129.25</v>
+        <v>123.15</v>
       </c>
       <c r="I26" t="n">
         <v>125.1608164857721</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K26" t="n">
-        <v>3.03</v>
+        <v>-1.83</v>
       </c>
       <c r="L26" t="n">
-        <v>2.27</v>
+        <v>2.99</v>
       </c>
       <c r="M26" t="n">
         <v>2</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>17.67</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43727</v>
+        <v>43728</v>
       </c>
       <c r="H27" t="n">
-        <v>123.3</v>
+        <v>127.75</v>
       </c>
       <c r="I27" t="n">
         <v>126.9182828439331</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.12</v>
+        <v>-3.74</v>
       </c>
       <c r="L27" t="n">
         <v>6.82</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>13.61</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43797</v>
+        <v>43798</v>
       </c>
       <c r="H28" t="n">
-        <v>158.25</v>
+        <v>154.4</v>
       </c>
       <c r="I28" t="n">
         <v>155.2665163562188</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K28" t="n">
-        <v>23.87</v>
+        <v>20.86</v>
       </c>
       <c r="L28" t="n">
         <v>6.58</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -2073,25 +2420,25 @@
         <v>11.31</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43810</v>
+        <v>43811</v>
       </c>
       <c r="H29" t="n">
-        <v>165.9</v>
+        <v>173.2</v>
       </c>
       <c r="I29" t="n">
         <v>169.7417848058549</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K29" t="n">
-        <v>-7.45</v>
+        <v>-12.18</v>
       </c>
       <c r="L29" t="n">
-        <v>7.84</v>
+        <v>12.6</v>
       </c>
       <c r="M29" t="n">
-        <v>0.51</v>
+        <v>0.57</v>
       </c>
       <c r="N29" t="n">
         <v>5.67</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>11.98</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43865</v>
+        <v>43866</v>
       </c>
       <c r="H30" t="n">
-        <v>172.7</v>
+        <v>168.75</v>
       </c>
       <c r="I30" t="n">
         <v>172.1996438645999</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.29</v>
+        <v>-2.57</v>
       </c>
       <c r="L30" t="n">
         <v>4.1</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>14.21</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43948</v>
+        <v>43949</v>
       </c>
       <c r="H31" t="n">
-        <v>114.4</v>
+        <v>129.75</v>
       </c>
       <c r="I31" t="n">
         <v>125.1290076031771</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K31" t="n">
-        <v>32.21</v>
+        <v>23.11</v>
       </c>
       <c r="L31" t="n">
         <v>7.5</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>28.86</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44042</v>
+        <v>44043</v>
       </c>
       <c r="H32" t="n">
-        <v>164.2</v>
+        <v>158.5</v>
       </c>
       <c r="I32" t="n">
         <v>161.1471545375333</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K32" t="n">
-        <v>26.55</v>
+        <v>22.16</v>
       </c>
       <c r="L32" t="n">
         <v>14.26</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>5</v>
+      </c>
+      <c r="U32" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="33">
@@ -2301,25 +2696,25 @@
         <v>18.21</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44088</v>
+        <v>44089</v>
       </c>
       <c r="H33" t="n">
-        <v>158.75</v>
+        <v>160.2</v>
       </c>
       <c r="I33" t="n">
         <v>160.1311716989253</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.16</v>
+        <v>-1.07</v>
       </c>
       <c r="L33" t="n">
         <v>6.62</v>
       </c>
       <c r="M33" t="n">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="N33" t="n">
         <v>6.75</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>12.88</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44097</v>
+        <v>44098</v>
       </c>
       <c r="H34" t="n">
-        <v>146.35</v>
+        <v>140.8</v>
       </c>
       <c r="I34" t="n">
         <v>144.0834633580363</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K34" t="n">
-        <v>-8.65</v>
+        <v>-12.11</v>
       </c>
       <c r="L34" t="n">
-        <v>10.24</v>
+        <v>12.8</v>
       </c>
       <c r="M34" t="n">
         <v>1.37</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>15.24</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44104</v>
+        <v>44105</v>
       </c>
       <c r="H35" t="n">
-        <v>157.15</v>
+        <v>166.45</v>
       </c>
       <c r="I35" t="n">
         <v>162.2636871907924</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K35" t="n">
-        <v>-11.61</v>
+        <v>-18.22</v>
       </c>
       <c r="L35" t="n">
-        <v>14.95</v>
+        <v>18.79</v>
       </c>
       <c r="M35" t="n">
         <v>2.81</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>15.01</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44218</v>
+        <v>44221</v>
       </c>
       <c r="H36" t="n">
-        <v>162.1</v>
+        <v>160.3</v>
       </c>
       <c r="I36" t="n">
         <v>161.3981709060029</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="K36" t="n">
-        <v>-2.61</v>
+        <v>-3.69</v>
       </c>
       <c r="L36" t="n">
         <v>8.08</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>4</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>11.43</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44229</v>
+        <v>44230</v>
       </c>
       <c r="H37" t="n">
-        <v>169.75</v>
+        <v>172.85</v>
       </c>
       <c r="I37" t="n">
         <v>172.2040909670194</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K37" t="n">
-        <v>-5.9</v>
+        <v>-7.83</v>
       </c>
       <c r="L37" t="n">
-        <v>7.74</v>
+        <v>9.23</v>
       </c>
       <c r="M37" t="n">
         <v>2.15</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>12.04</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44271</v>
+        <v>44272</v>
       </c>
       <c r="H38" t="n">
-        <v>163.9</v>
+        <v>159.4</v>
       </c>
       <c r="I38" t="n">
         <v>159.6498828293707</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K38" t="n">
-        <v>-5.18</v>
+        <v>-7.78</v>
       </c>
       <c r="L38" t="n">
-        <v>8.1</v>
+        <v>8.24</v>
       </c>
       <c r="M38" t="n">
         <v>2.93</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>12.86</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44337</v>
+        <v>44340</v>
       </c>
       <c r="H39" t="n">
-        <v>159.65</v>
+        <v>160.35</v>
       </c>
       <c r="I39" t="n">
         <v>160.3137776118778</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.16</v>
+        <v>-0.6</v>
       </c>
       <c r="L39" t="n">
         <v>3.83</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>8.460000000000001</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44417</v>
+        <v>44418</v>
       </c>
       <c r="H40" t="n">
-        <v>200.9</v>
+        <v>191.5</v>
       </c>
       <c r="I40" t="n">
         <v>191.7980591490078</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K40" t="n">
-        <v>25.29</v>
+        <v>19.43</v>
       </c>
       <c r="L40" t="n">
         <v>4.27</v>
@@ -2721,7 +3200,7 @@
         <v>2.31</v>
       </c>
       <c r="N40" t="n">
-        <v>3.84</v>
+        <v>4.68</v>
       </c>
       <c r="O40" t="n">
         <v>0.44</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4</v>
+      </c>
+      <c r="U40" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>15.23</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44469</v>
+        <v>44470</v>
       </c>
       <c r="H41" t="n">
-        <v>169.15</v>
+        <v>179.55</v>
       </c>
       <c r="I41" t="n">
         <v>176.9227152594012</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K41" t="n">
-        <v>11.67</v>
+        <v>6.24</v>
       </c>
       <c r="L41" t="n">
         <v>7.47</v>
@@ -2778,7 +3269,7 @@
         <v>1.07</v>
       </c>
       <c r="N41" t="n">
-        <v>3.19</v>
+        <v>6.15</v>
       </c>
       <c r="O41" t="n">
         <v>-4.68</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>12.56</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44515</v>
+        <v>44516</v>
       </c>
       <c r="H42" t="n">
-        <v>197.1</v>
+        <v>189.5</v>
       </c>
       <c r="I42" t="n">
         <v>195.4491053290388</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K42" t="n">
-        <v>9.77</v>
+        <v>5.54</v>
       </c>
       <c r="L42" t="n">
         <v>5.65</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>17.16</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44760</v>
+        <v>44761</v>
       </c>
       <c r="H43" t="n">
-        <v>93.15000000000001</v>
+        <v>94.5</v>
       </c>
       <c r="I43" t="n">
         <v>94.46305829478356</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K43" t="n">
-        <v>50.84</v>
+        <v>50.13</v>
       </c>
       <c r="L43" t="n">
         <v>4.56</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>168</v>
+        <v>169</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>9</v>
+      </c>
+      <c r="U43" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>10.54</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44826</v>
+        <v>44827</v>
       </c>
       <c r="H44" t="n">
-        <v>97.75</v>
+        <v>95.05</v>
       </c>
       <c r="I44" t="n">
         <v>97.13549462123069</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K44" t="n">
-        <v>3.44</v>
+        <v>0.58</v>
       </c>
       <c r="L44" t="n">
         <v>4.71</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>11.65</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44845</v>
+        <v>44846</v>
       </c>
       <c r="H45" t="n">
-        <v>99.2</v>
+        <v>104.1</v>
       </c>
       <c r="I45" t="n">
         <v>102.4335064456359</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K45" t="n">
-        <v>-4.37</v>
+        <v>-9.52</v>
       </c>
       <c r="L45" t="n">
-        <v>8.050000000000001</v>
+        <v>10.05</v>
       </c>
       <c r="M45" t="n">
         <v>2.51</v>
       </c>
       <c r="N45" t="n">
-        <v>3.51</v>
+        <v>4.94</v>
       </c>
       <c r="O45" t="n">
         <v>-2.76</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>11.58</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44917</v>
+        <v>44918</v>
       </c>
       <c r="H46" t="n">
-        <v>114.1</v>
+        <v>108.15</v>
       </c>
       <c r="I46" t="n">
         <v>113.1128676608117</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K46" t="n">
-        <v>9.609999999999999</v>
+        <v>3.89</v>
       </c>
       <c r="L46" t="n">
         <v>4.51</v>
@@ -3063,7 +3614,7 @@
         <v>2.18</v>
       </c>
       <c r="N46" t="n">
-        <v>3.66</v>
+        <v>5.21</v>
       </c>
       <c r="O46" t="n">
         <v>4.94</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>13.7</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44928</v>
+        <v>44929</v>
       </c>
       <c r="H47" t="n">
-        <v>119.35</v>
+        <v>122.1</v>
       </c>
       <c r="I47" t="n">
         <v>121.2917123432758</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K47" t="n">
-        <v>-10.36</v>
+        <v>-12.9</v>
       </c>
       <c r="L47" t="n">
-        <v>11.05</v>
+        <v>13.41</v>
       </c>
       <c r="M47" t="n">
         <v>0.86</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>11.02</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44951</v>
+        <v>44953</v>
       </c>
       <c r="H48" t="n">
-        <v>115.25</v>
+        <v>112.45</v>
       </c>
       <c r="I48" t="n">
         <v>112.9881230679012</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K48" t="n">
-        <v>-5.61</v>
+        <v>-7.9</v>
       </c>
       <c r="L48" t="n">
-        <v>7.45</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="M48" t="n">
         <v>0.3</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>11.11</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44991</v>
+        <v>44993</v>
       </c>
       <c r="H49" t="n">
-        <v>110.4</v>
+        <v>113.6</v>
       </c>
       <c r="I49" t="n">
         <v>111.445779541067</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K49" t="n">
-        <v>1.82</v>
+        <v>-1.02</v>
       </c>
       <c r="L49" t="n">
         <v>5.56</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>10.48</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45048</v>
+        <v>45049</v>
       </c>
       <c r="H50" t="n">
-        <v>129.7</v>
+        <v>113.95</v>
       </c>
       <c r="I50" t="n">
         <v>120.026544856946</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K50" t="n">
-        <v>14.17</v>
+        <v>0.31</v>
       </c>
       <c r="L50" t="n">
         <v>4.62</v>
@@ -3291,7 +3890,7 @@
         <v>1.22</v>
       </c>
       <c r="N50" t="n">
-        <v>3.37</v>
+        <v>12.14</v>
       </c>
       <c r="O50" t="n">
         <v>2.9</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>18.08</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45089</v>
+        <v>45090</v>
       </c>
       <c r="H51" t="n">
-        <v>118.75</v>
+        <v>121.5</v>
       </c>
       <c r="I51" t="n">
         <v>120.4916003231198</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K51" t="n">
-        <v>-4.21</v>
+        <v>-6.63</v>
       </c>
       <c r="L51" t="n">
         <v>13.82</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>9.52</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45180</v>
+        <v>45181</v>
       </c>
       <c r="H52" t="n">
-        <v>148.5</v>
+        <v>138.35</v>
       </c>
       <c r="I52" t="n">
         <v>138.8442305284334</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K52" t="n">
-        <v>22.22</v>
+        <v>13.87</v>
       </c>
       <c r="L52" t="n">
         <v>2.55</v>
@@ -3405,7 +4028,7 @@
         <v>2.66</v>
       </c>
       <c r="N52" t="n">
-        <v>4.59</v>
+        <v>6.84</v>
       </c>
       <c r="O52" t="n">
         <v>2.32</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>4</v>
+      </c>
+      <c r="U52" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>16.34</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45243</v>
+        <v>45245</v>
       </c>
       <c r="H53" t="n">
-        <v>140.35</v>
+        <v>150.5</v>
       </c>
       <c r="I53" t="n">
         <v>146.4523476727501</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K53" t="n">
-        <v>-1.45</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="L53" t="n">
-        <v>9.720000000000001</v>
+        <v>11.56</v>
       </c>
       <c r="M53" t="n">
-        <v>2</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="N53" t="n">
-        <v>4.88</v>
+        <v>7.23</v>
       </c>
       <c r="O53" t="n">
         <v>-6.84</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>10.91</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45358</v>
+        <v>45362</v>
       </c>
       <c r="H54" t="n">
-        <v>172.4</v>
+        <v>169.25</v>
       </c>
       <c r="I54" t="n">
         <v>172.2040512209436</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="K54" t="n">
-        <v>14.55</v>
+        <v>12.46</v>
       </c>
       <c r="L54" t="n">
         <v>2.23</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>5</v>
+      </c>
+      <c r="U54" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>14.31</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="H55" t="n">
-        <v>183.85</v>
+        <v>194.05</v>
       </c>
       <c r="I55" t="n">
         <v>187.462003130626</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K55" t="n">
-        <v>-8.630000000000001</v>
+        <v>-14.65</v>
       </c>
       <c r="L55" t="n">
-        <v>9.48</v>
+        <v>15.45</v>
       </c>
       <c r="M55" t="n">
         <v>1.56</v>
       </c>
       <c r="N55" t="n">
-        <v>5.05</v>
+        <v>5.55</v>
       </c>
       <c r="O55" t="n">
         <v>-1.83</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>13.17</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45419</v>
+        <v>45420</v>
       </c>
       <c r="H56" t="n">
-        <v>185.65</v>
+        <v>180</v>
       </c>
       <c r="I56" t="n">
         <v>183.3436108944572</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K56" t="n">
-        <v>-4.33</v>
+        <v>-7.24</v>
       </c>
       <c r="L56" t="n">
-        <v>6.42</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="M56" t="n">
         <v>2.91</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>13.15</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45455</v>
+        <v>45456</v>
       </c>
       <c r="H57" t="n">
-        <v>184.69</v>
+        <v>186.77</v>
       </c>
       <c r="I57" t="n">
         <v>186.4719103018548</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K57" t="n">
-        <v>-2.61</v>
+        <v>-3.76</v>
       </c>
       <c r="L57" t="n">
         <v>4.64</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>9.98</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45495</v>
+        <v>45496</v>
       </c>
       <c r="H58" t="n">
-        <v>215.27</v>
+        <v>202.73</v>
       </c>
       <c r="I58" t="n">
         <v>204.6642003122374</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K58" t="n">
-        <v>15.26</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="L58" t="n">
         <v>1.27</v>
@@ -3747,7 +4442,7 @@
         <v>0.44</v>
       </c>
       <c r="N58" t="n">
-        <v>5.14</v>
+        <v>5.83</v>
       </c>
       <c r="O58" t="n">
         <v>1.13</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>15.66</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45629</v>
+        <v>45630</v>
       </c>
       <c r="H59" t="n">
-        <v>164.19</v>
+        <v>169.59</v>
       </c>
       <c r="I59" t="n">
         <v>168.9976511180872</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K59" t="n">
-        <v>19.01</v>
+        <v>16.35</v>
       </c>
       <c r="L59" t="n">
         <v>9.6</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>6</v>
+      </c>
+      <c r="U59" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>12.05</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45701</v>
+        <v>45702</v>
       </c>
       <c r="H60" t="n">
-        <v>194.06</v>
+        <v>178.15</v>
       </c>
       <c r="I60" t="n">
         <v>183.4661257161414</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K60" t="n">
-        <v>14.43</v>
+        <v>5.05</v>
       </c>
       <c r="L60" t="n">
         <v>3.63</v>
       </c>
       <c r="M60" t="n">
-        <v>2.67</v>
+        <v>3.12</v>
       </c>
       <c r="N60" t="n">
-        <v>6.23</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O60" t="n">
         <v>3.29</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>17.81</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45733</v>
+        <v>45734</v>
       </c>
       <c r="H61" t="n">
-        <v>209.62</v>
+        <v>211.21</v>
       </c>
       <c r="I61" t="n">
         <v>209.8867094632881</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K61" t="n">
-        <v>-17.66</v>
+        <v>-18.56</v>
       </c>
       <c r="L61" t="n">
-        <v>20.1</v>
+        <v>20.11</v>
       </c>
       <c r="M61" t="n">
         <v>3.85</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>11.27</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45868</v>
+        <v>45869</v>
       </c>
       <c r="H62" t="n">
-        <v>256.55</v>
+        <v>253.05</v>
       </c>
       <c r="I62" t="n">
         <v>256.3843329068104</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K62" t="n">
-        <v>21.47</v>
+        <v>19.81</v>
       </c>
       <c r="L62" t="n">
         <v>1.66</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>5</v>
+      </c>
+      <c r="U62" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>7.82</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45898</v>
+        <v>45901</v>
       </c>
       <c r="H63" t="n">
-        <v>261.45</v>
+        <v>275</v>
       </c>
       <c r="I63" t="n">
         <v>270.4863786856718</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K63" t="n">
-        <v>-3.32</v>
+        <v>-8.67</v>
       </c>
       <c r="L63" t="n">
-        <v>8.52</v>
+        <v>9.01</v>
       </c>
       <c r="M63" t="n">
         <v>1.6</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,25 +4835,25 @@
         <v>10.66</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="H64" t="n">
-        <v>274.9</v>
+        <v>269.5</v>
       </c>
       <c r="I64" t="n">
         <v>273.588917068346</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K64" t="n">
-        <v>-0.04</v>
+        <v>-2</v>
       </c>
       <c r="L64" t="n">
         <v>4.64</v>
       </c>
       <c r="M64" t="n">
-        <v>1.42</v>
+        <v>3.56</v>
       </c>
       <c r="N64" t="n">
         <v>3.23</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>3</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>9.220000000000001</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="H65" t="n">
-        <v>287.05</v>
+        <v>292.65</v>
       </c>
       <c r="I65" t="n">
         <v>290.7138566976164</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K65" t="n">
-        <v>-6.51</v>
+        <v>-8.59</v>
       </c>
       <c r="L65" t="n">
-        <v>8.35</v>
+        <v>9.09</v>
       </c>
       <c r="M65" t="n">
         <v>1.52</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>8.15</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="H66" t="n">
-        <v>309.5</v>
+        <v>285.85</v>
       </c>
       <c r="I66" t="n">
         <v>290.5309677304327</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K66" t="n">
-        <v>5.76</v>
+        <v>-2.32</v>
       </c>
       <c r="L66" t="n">
-        <v>2.7</v>
+        <v>4.82</v>
       </c>
       <c r="M66" t="n">
         <v>0.74</v>
       </c>
       <c r="N66" t="n">
-        <v>3.25</v>
+        <v>7.64</v>
       </c>
       <c r="O66" t="n">
         <v>1.95</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>15.59</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="H67" t="n">
-        <v>281.8</v>
+        <v>295.05</v>
       </c>
       <c r="I67" t="n">
         <v>282.4744870989085</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K67" t="n">
-        <v>1.42</v>
+        <v>-3.22</v>
       </c>
       <c r="L67" t="n">
         <v>11.19</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>4</v>
+      </c>
+      <c r="U67" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>11.46</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="H68" t="n">
-        <v>308.2</v>
+        <v>299.2</v>
       </c>
       <c r="I68" t="n">
         <v>300.411511643521</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K68" t="n">
-        <v>4.46</v>
+        <v>1.41</v>
       </c>
       <c r="L68" t="n">
         <v>4.66</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>3</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>10.55</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="H69" t="n">
-        <v>319.05</v>
+        <v>321.35</v>
       </c>
       <c r="I69" t="n">
         <v>320.2318311507416</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K69" t="n">
-        <v>-6.63</v>
+        <v>-7.4</v>
       </c>
       <c r="L69" t="n">
-        <v>7.59</v>
+        <v>7.77</v>
       </c>
       <c r="M69" t="n">
         <v>2.47</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>9.220000000000001</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="H70" t="n">
-        <v>346.6</v>
+        <v>340</v>
       </c>
       <c r="I70" t="n">
         <v>341.9544617555862</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K70" t="n">
-        <v>7.86</v>
+        <v>5.8</v>
       </c>
       <c r="L70" t="n">
         <v>4.81</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>3</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -4491,6 +5342,14 @@
       <c r="Q71" t="n">
         <v>48</v>
       </c>
+      <c r="R71" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9449,7 +10308,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>60.1</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="6">
@@ -9459,7 +10318,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
@@ -9469,7 +10328,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="8">
@@ -9479,7 +10338,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -9489,7 +10348,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10">
@@ -9499,7 +10358,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>104.2</v>
+        <v>105.6</v>
       </c>
     </row>
     <row r="11">
@@ -9509,7 +10368,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
@@ -9519,7 +10378,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13">
@@ -9529,7 +10388,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>27.5</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="14">
@@ -9539,7 +10398,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8.9</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="15">
@@ -9549,7 +10408,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15.61</v>
+        <v>10.14</v>
       </c>
     </row>
     <row r="16">
@@ -9559,7 +10418,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.99</v>
+        <v>-1.94</v>
       </c>
     </row>
     <row r="17">
@@ -9569,7 +10428,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>305.16</v>
+        <v>257.54</v>
       </c>
     </row>
     <row r="18">
@@ -9579,7 +10438,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>50.7</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="19">
@@ -9589,7 +10448,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -9599,7 +10458,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.82</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="21">
@@ -9619,7 +10478,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23">
@@ -9629,7 +10488,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24">
@@ -9639,7 +10498,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.65</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="25">
@@ -9659,7 +10518,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.43</v>
+        <v>6.16</v>
       </c>
     </row>
     <row r="27">
@@ -9679,7 +10538,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29">
